--- a/src/assets/static files/Change_Bill_Day.xlsx
+++ b/src/assets/static files/Change_Bill_Day.xlsx
@@ -15,21 +15,19 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Loan ID</t>
   </si>
   <si>
     <t>New Bill Day</t>
+  </si>
+  <si>
+    <t>FPL-00000000001</t>
   </si>
 </sst>
 </file>
@@ -68,12 +66,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -374,8 +373,12 @@
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
+      <c r="A2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5">
+        <v>10</v>
+      </c>
       <c r="C2" s="2"/>
       <c r="F2" s="3"/>
       <c r="G2" s="4"/>
